--- a/docs/achievements-v7-proposal.xlsx
+++ b/docs/achievements-v7-proposal.xlsx
@@ -610,7 +610,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>All 101 current achievements plus 5 proposed additions, assessed against the design rubric below. Nothing here is implemented - this is the sheet to argue with.</t>
+          <t>All 101 pre-v7 achievements plus the 5 proposed additions, assessed against the design rubric below. This began as a sheet to argue with and is now the RECORD of what was decided: v7 is built, checked and verified on a Pixel 7. The code is the source of truth - nothing reads this file.</t>
         </is>
       </c>
       <c r="B5" s="2" t="n"/>
@@ -791,7 +791,7 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>Y = in the proposed list. REVISED after your first pass: GALLERY! accepted, DOUBLING! and THIRD! rejected. That makes 3 additions against 2 drops, so the list currently reads 102 and needs one more drop - see DECISION NEEDED on the Distribution tab. Everything marked REVIEW is still Y; it stays unless you say otherwise.</t>
+          <t>Y = in the shipped list. GALLERY! was accepted; DOUBLING! and THIRD! rejected; WHOLE! dropped as the third cut so the total holds at 101 and XP at 2000. Everything marked REVIEW stayed in - those were never decided, and remain open.</t>
         </is>
       </c>
     </row>
@@ -1116,7 +1116,7 @@
       <c r="P3" s="6" t="inlineStr"/>
       <c r="Q3" s="8" t="inlineStr">
         <is>
-          <t>Natural number</t>
+          <t>https://en.wikipedia.org/wiki/Natural_number</t>
         </is>
       </c>
       <c r="R3" s="6" t="inlineStr">
@@ -1190,7 +1190,7 @@
       <c r="P4" s="6" t="inlineStr"/>
       <c r="Q4" s="8" t="inlineStr">
         <is>
-          <t>Phyllotaxis</t>
+          <t>https://en.wikipedia.org/wiki/Phyllotaxis</t>
         </is>
       </c>
       <c r="R4" s="6" t="inlineStr">
@@ -2006,7 +2006,7 @@
       <c r="P16" s="6" t="inlineStr"/>
       <c r="Q16" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>https://en.wikipedia.org/wiki/1</t>
         </is>
       </c>
       <c r="R16" s="6" t="inlineStr">
@@ -2080,7 +2080,7 @@
       <c r="P17" s="6" t="inlineStr"/>
       <c r="Q17" s="8" t="inlineStr">
         <is>
-          <t>Empty set</t>
+          <t>https://en.wikipedia.org/wiki/Empty_set</t>
         </is>
       </c>
       <c r="R17" s="6" t="inlineStr"/>
@@ -2150,7 +2150,7 @@
       <c r="P18" s="6" t="inlineStr"/>
       <c r="Q18" s="8" t="inlineStr">
         <is>
-          <t>Fibonacci sequence</t>
+          <t>https://en.wikipedia.org/wiki/Fibonacci_sequence</t>
         </is>
       </c>
       <c r="R18" s="6" t="inlineStr">
@@ -2228,7 +2228,7 @@
       <c r="P19" s="6" t="inlineStr"/>
       <c r="Q19" s="8" t="inlineStr">
         <is>
-          <t>Lucas number</t>
+          <t>https://en.wikipedia.org/wiki/Lucas_number</t>
         </is>
       </c>
       <c r="R19" s="6" t="inlineStr">
@@ -2302,7 +2302,7 @@
       <c r="P20" s="6" t="inlineStr"/>
       <c r="Q20" s="8" t="inlineStr">
         <is>
-          <t>Perfect number</t>
+          <t>https://en.wikipedia.org/wiki/Perfect_number</t>
         </is>
       </c>
       <c r="R20" s="6" t="inlineStr">
@@ -2376,7 +2376,7 @@
       <c r="P21" s="6" t="inlineStr"/>
       <c r="Q21" s="8" t="inlineStr">
         <is>
-          <t>Twin prime</t>
+          <t>https://en.wikipedia.org/wiki/Twin_prime</t>
         </is>
       </c>
       <c r="R21" s="6" t="inlineStr">
@@ -2450,7 +2450,7 @@
       <c r="P22" s="6" t="inlineStr"/>
       <c r="Q22" s="8" t="inlineStr">
         <is>
-          <t>Cousin prime</t>
+          <t>https://en.wikipedia.org/wiki/Cousin_prime</t>
         </is>
       </c>
       <c r="R22" s="6" t="inlineStr"/>
@@ -2520,7 +2520,7 @@
       <c r="P23" s="6" t="inlineStr"/>
       <c r="Q23" s="8" t="inlineStr">
         <is>
-          <t>Sexy primes</t>
+          <t>https://en.wikipedia.org/wiki/Sexy_primes</t>
         </is>
       </c>
       <c r="R23" s="6" t="inlineStr"/>
@@ -2590,7 +2590,7 @@
       <c r="P24" s="6" t="inlineStr"/>
       <c r="Q24" s="8" t="inlineStr">
         <is>
-          <t>Safe and Sophie Germain primes</t>
+          <t>https://en.wikipedia.org/wiki/Safe_and_Sophie_Germain_primes</t>
         </is>
       </c>
       <c r="R24" s="6" t="inlineStr">
@@ -2664,7 +2664,7 @@
       <c r="P25" s="6" t="inlineStr"/>
       <c r="Q25" s="8" t="inlineStr">
         <is>
-          <t>Emirp</t>
+          <t>https://en.wikipedia.org/wiki/Emirp</t>
         </is>
       </c>
       <c r="R25" s="6" t="inlineStr"/>
@@ -2736,11 +2736,7 @@
         </is>
       </c>
       <c r="P26" s="6" t="inlineStr"/>
-      <c r="Q26" s="8" t="inlineStr">
-        <is>
-          <t>Mersenne prime</t>
-        </is>
-      </c>
+      <c r="Q26" s="6" t="inlineStr"/>
       <c r="R26" s="6" t="inlineStr">
         <is>
           <t>Same idea as PERFECT! (2^p - 1), and the weaker of the two: PERFECT! reveals 6, 28 and 496, while MERSENNE! gilds back the four primes you just tapped. PERFECT!’s blurb already explains Mersenne primes, so the subject survives the cut. Frees the slot for TEMPTED!.</t>
@@ -2812,7 +2808,7 @@
       <c r="P27" s="6" t="inlineStr"/>
       <c r="Q27" s="8" t="inlineStr">
         <is>
-          <t>Fermat number</t>
+          <t>https://en.wikipedia.org/wiki/Fermat_number</t>
         </is>
       </c>
       <c r="R27" s="6" t="inlineStr">
@@ -2886,7 +2882,7 @@
       <c r="P28" s="6" t="inlineStr"/>
       <c r="Q28" s="8" t="inlineStr">
         <is>
-          <t>Golden angle</t>
+          <t>https://en.wikipedia.org/wiki/Golden_angle</t>
         </is>
       </c>
       <c r="R28" s="6" t="inlineStr">
@@ -2960,7 +2956,7 @@
       <c r="P29" s="6" t="inlineStr"/>
       <c r="Q29" s="8" t="inlineStr">
         <is>
-          <t>Up to eleven</t>
+          <t>https://en.wikipedia.org/wiki/Up_to_eleven</t>
         </is>
       </c>
       <c r="R29" s="6" t="inlineStr">
@@ -3034,7 +3030,7 @@
       <c r="P30" s="6" t="inlineStr"/>
       <c r="Q30" s="8" t="inlineStr">
         <is>
-          <t>101 (number)</t>
+          <t>https://en.wikipedia.org/wiki/101_%28number%29</t>
         </is>
       </c>
       <c r="R30" s="6" t="inlineStr"/>
@@ -3108,7 +3104,7 @@
       <c r="P31" s="6" t="inlineStr"/>
       <c r="Q31" s="8" t="inlineStr">
         <is>
-          <t>Balanced prime</t>
+          <t>https://en.wikipedia.org/wiki/Balanced_prime</t>
         </is>
       </c>
       <c r="R31" s="6" t="inlineStr">
@@ -3186,7 +3182,7 @@
       <c r="P32" s="6" t="inlineStr"/>
       <c r="Q32" s="8" t="inlineStr">
         <is>
-          <t>Prime gap</t>
+          <t>https://en.wikipedia.org/wiki/Prime_gap</t>
         </is>
       </c>
       <c r="R32" s="6" t="inlineStr">
@@ -3264,7 +3260,7 @@
       <c r="P33" s="6" t="inlineStr"/>
       <c r="Q33" s="8" t="inlineStr">
         <is>
-          <t>Decimal</t>
+          <t>https://en.wikipedia.org/wiki/Decimal</t>
         </is>
       </c>
       <c r="R33" s="6" t="inlineStr">
@@ -3338,7 +3334,7 @@
       <c r="P34" s="6" t="inlineStr"/>
       <c r="Q34" s="8" t="inlineStr">
         <is>
-          <t>Super-prime</t>
+          <t>https://en.wikipedia.org/wiki/Super-prime</t>
         </is>
       </c>
       <c r="R34" s="6" t="inlineStr">
@@ -3412,7 +3408,7 @@
       <c r="P35" s="6" t="inlineStr"/>
       <c r="Q35" s="8" t="inlineStr">
         <is>
-          <t>Goldbach's conjecture</t>
+          <t>https://en.wikipedia.org/wiki/Goldbach%27s_conjecture</t>
         </is>
       </c>
       <c r="R35" s="6" t="inlineStr">
@@ -3490,7 +3486,7 @@
       <c r="P36" s="6" t="inlineStr"/>
       <c r="Q36" s="8" t="inlineStr">
         <is>
-          <t>Collatz conjecture</t>
+          <t>https://en.wikipedia.org/wiki/Collatz_conjecture</t>
         </is>
       </c>
       <c r="R36" s="6" t="inlineStr">
@@ -3564,7 +3560,7 @@
       <c r="P37" s="6" t="inlineStr"/>
       <c r="Q37" s="8" t="inlineStr">
         <is>
-          <t>Prime number</t>
+          <t>https://en.wikipedia.org/wiki/Prime_number</t>
         </is>
       </c>
       <c r="R37" s="6" t="inlineStr"/>
@@ -3634,7 +3630,7 @@
       <c r="P38" s="6" t="inlineStr"/>
       <c r="Q38" s="8" t="inlineStr">
         <is>
-          <t>Primes in arithmetic progression</t>
+          <t>https://en.wikipedia.org/wiki/Primes_in_arithmetic_progression</t>
         </is>
       </c>
       <c r="R38" s="6" t="inlineStr">
@@ -3708,7 +3704,7 @@
       <c r="P39" s="6" t="inlineStr"/>
       <c r="Q39" s="8" t="inlineStr">
         <is>
-          <t>Square number</t>
+          <t>https://en.wikipedia.org/wiki/Square_number</t>
         </is>
       </c>
       <c r="R39" s="6" t="inlineStr"/>
@@ -3776,11 +3772,7 @@
         </is>
       </c>
       <c r="P40" s="6" t="inlineStr"/>
-      <c r="Q40" s="8" t="inlineStr">
-        <is>
-          <t>69 (number)</t>
-        </is>
-      </c>
+      <c r="Q40" s="6" t="inlineStr"/>
       <c r="R40" s="6" t="inlineStr"/>
     </row>
     <row r="41">
@@ -3848,7 +3840,7 @@
       <c r="P41" s="6" t="inlineStr"/>
       <c r="Q41" s="8" t="inlineStr">
         <is>
-          <t>420 (cannabis culture)</t>
+          <t>https://en.wikipedia.org/wiki/420_%28number%29</t>
         </is>
       </c>
       <c r="R41" s="6" t="inlineStr"/>
@@ -3986,11 +3978,7 @@
         </is>
       </c>
       <c r="P43" s="6" t="inlineStr"/>
-      <c r="Q43" s="8" t="inlineStr">
-        <is>
-          <t>Calculator spelling</t>
-        </is>
-      </c>
+      <c r="Q43" s="6" t="inlineStr"/>
       <c r="R43" s="6" t="inlineStr"/>
     </row>
     <row r="44">
@@ -4058,7 +4046,7 @@
       <c r="P44" s="6" t="inlineStr"/>
       <c r="Q44" s="8" t="inlineStr">
         <is>
-          <t>Catch-22 (logic)</t>
+          <t>https://en.wikipedia.org/wiki/Catch-22_%28logic%29</t>
         </is>
       </c>
       <c r="R44" s="6" t="inlineStr">
@@ -4132,7 +4120,7 @@
       <c r="P45" s="6" t="inlineStr"/>
       <c r="Q45" s="8" t="inlineStr">
         <is>
-          <t>U.S. Route 66</t>
+          <t>https://en.wikipedia.org/wiki/U.S._Route_66</t>
         </is>
       </c>
       <c r="R45" s="6" t="inlineStr">
@@ -4210,7 +4198,7 @@
       </c>
       <c r="Q46" s="8" t="inlineStr">
         <is>
-          <t>Blackjack</t>
+          <t>https://en.wikipedia.org/wiki/21_%28number%29</t>
         </is>
       </c>
       <c r="R46" s="6" t="inlineStr">
@@ -4284,7 +4272,7 @@
       <c r="P47" s="6" t="inlineStr"/>
       <c r="Q47" s="8" t="inlineStr">
         <is>
-          <t>Slot machine</t>
+          <t>https://en.wikipedia.org/wiki/777_%28number%29</t>
         </is>
       </c>
       <c r="R47" s="6" t="inlineStr"/>
@@ -4354,7 +4342,7 @@
       <c r="P48" s="6" t="inlineStr"/>
       <c r="Q48" s="8" t="inlineStr">
         <is>
-          <t>57 (number)</t>
+          <t>https://en.wikipedia.org/wiki/57_%28number%29</t>
         </is>
       </c>
       <c r="R48" s="6" t="inlineStr">
@@ -4428,7 +4416,7 @@
       <c r="P49" s="6" t="inlineStr"/>
       <c r="Q49" s="8" t="inlineStr">
         <is>
-          <t>Slurpee</t>
+          <t>https://en.wikipedia.org/wiki/Slurpee</t>
         </is>
       </c>
       <c r="R49" s="6" t="inlineStr"/>
@@ -4498,7 +4486,7 @@
       <c r="P50" s="6" t="inlineStr"/>
       <c r="Q50" s="8" t="inlineStr">
         <is>
-          <t>Battle of Thermopylae</t>
+          <t>https://en.wikipedia.org/wiki/Battle_of_Thermopylae</t>
         </is>
       </c>
       <c r="R50" s="6" t="inlineStr"/>
@@ -4568,7 +4556,7 @@
       <c r="P51" s="6" t="inlineStr"/>
       <c r="Q51" s="8" t="inlineStr">
         <is>
-          <t>Boeing 747</t>
+          <t>https://en.wikipedia.org/wiki/Boeing_747</t>
         </is>
       </c>
       <c r="R51" s="6" t="inlineStr"/>
@@ -4638,7 +4626,7 @@
       <c r="P52" s="6" t="inlineStr"/>
       <c r="Q52" s="8" t="inlineStr">
         <is>
-          <t>Standard 52-card deck</t>
+          <t>https://en.wikipedia.org/wiki/Standard_52-card_deck</t>
         </is>
       </c>
       <c r="R52" s="6" t="inlineStr">
@@ -4712,7 +4700,7 @@
       <c r="P53" s="6" t="inlineStr"/>
       <c r="Q53" s="8" t="inlineStr">
         <is>
-          <t>Number of the beast</t>
+          <t>https://en.wikipedia.org/wiki/Number_of_the_beast</t>
         </is>
       </c>
       <c r="R53" s="6" t="inlineStr">
@@ -4786,7 +4774,7 @@
       <c r="P54" s="6" t="inlineStr"/>
       <c r="Q54" s="8" t="inlineStr">
         <is>
-          <t>Repdigit</t>
+          <t>https://en.wikipedia.org/wiki/Repdigit</t>
         </is>
       </c>
       <c r="R54" s="6" t="inlineStr">
@@ -4860,7 +4848,7 @@
       <c r="P55" s="6" t="inlineStr"/>
       <c r="Q55" s="8" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>https://en.wikipedia.org/wiki/7</t>
         </is>
       </c>
       <c r="R55" s="6" t="inlineStr"/>
@@ -4930,7 +4918,7 @@
       <c r="P56" s="6" t="inlineStr"/>
       <c r="Q56" s="8" t="inlineStr">
         <is>
-          <t>Triskaidekaphobia</t>
+          <t>https://en.wikipedia.org/wiki/Triskaidekaphobia</t>
         </is>
       </c>
       <c r="R56" s="6" t="inlineStr"/>
@@ -5000,7 +4988,7 @@
       <c r="P57" s="6" t="inlineStr"/>
       <c r="Q57" s="8" t="inlineStr">
         <is>
-          <t>23 enigma</t>
+          <t>https://en.wikipedia.org/wiki/23_%28number%29</t>
         </is>
       </c>
       <c r="R57" s="6" t="inlineStr">
@@ -5074,7 +5062,7 @@
       <c r="P58" s="6" t="inlineStr"/>
       <c r="Q58" s="8" t="inlineStr">
         <is>
-          <t>Scottish Rite</t>
+          <t>https://en.wikipedia.org/wiki/33_%28number%29</t>
         </is>
       </c>
       <c r="R58" s="6" t="inlineStr">
@@ -5107,17 +5095,21 @@
           <t>Lore</t>
         </is>
       </c>
-      <c r="F59" s="7" t="inlineStr">
-        <is>
-          <t>KEEP</t>
+      <c r="F59" s="9" t="inlineStr">
+        <is>
+          <t>DROP</t>
         </is>
       </c>
       <c r="G59" s="6" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="H59" s="6" t="inlineStr"/>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="H59" s="6" t="inlineStr">
+        <is>
+          <t>GALLERY!</t>
+        </is>
+      </c>
       <c r="I59" s="6" t="inlineStr">
         <is>
           <t>select exactly {3, 31}</t>
@@ -5146,14 +5138,10 @@
         </is>
       </c>
       <c r="P59" s="6" t="inlineStr"/>
-      <c r="Q59" s="8" t="inlineStr">
-        <is>
-          <t>Thelema</t>
-        </is>
-      </c>
+      <c r="Q59" s="6" t="inlineStr"/>
       <c r="R59" s="6" t="inlineStr">
         <is>
-          <t>Thelema - the most inside reference in the list, and it has NO blurb. A player who does not already know gets "-do what thou wilt-" and the number 93, with no way to close the gap. Highest-priority blurb in the whole set.</t>
+          <t>DROPPED by Dakota, and it is the third drop that brought the list back to 101 once GALLERY! was accepted. It was the most inside reference in the list and had NO blurb, so a player who did not already know got "-do what thou wilt-" and the number 93 with no way to close the gap - the clearest case of the education tax the whole rubric exists to prevent.</t>
         </is>
       </c>
     </row>
@@ -5222,7 +5210,7 @@
       <c r="P60" s="6" t="inlineStr"/>
       <c r="Q60" s="8" t="inlineStr">
         <is>
-          <t>Number of the beast</t>
+          <t>https://en.wikipedia.org/wiki/Number_of_the_beast</t>
         </is>
       </c>
       <c r="R60" s="6" t="inlineStr">
@@ -5296,7 +5284,7 @@
       <c r="P61" s="6" t="inlineStr"/>
       <c r="Q61" s="8" t="inlineStr">
         <is>
-          <t>Sabbath</t>
+          <t>https://en.wikipedia.org/wiki/Sabbath</t>
         </is>
       </c>
       <c r="R61" s="6" t="inlineStr">
@@ -5370,7 +5358,7 @@
       <c r="P62" s="6" t="inlineStr"/>
       <c r="Q62" s="8" t="inlineStr">
         <is>
-          <t>Noble Eightfold Path</t>
+          <t>https://en.wikipedia.org/wiki/Noble_Eightfold_Path</t>
         </is>
       </c>
       <c r="R62" s="6" t="inlineStr">
@@ -5448,7 +5436,7 @@
       <c r="P63" s="6" t="inlineStr"/>
       <c r="Q63" s="8" t="inlineStr">
         <is>
-          <t>Sator Square</t>
+          <t>https://en.wikipedia.org/wiki/Palindromic_number</t>
         </is>
       </c>
       <c r="R63" s="6" t="inlineStr">
@@ -5522,7 +5510,7 @@
       <c r="P64" s="6" t="inlineStr"/>
       <c r="Q64" s="8" t="inlineStr">
         <is>
-          <t>Hierarchy of angels</t>
+          <t>https://en.wikipedia.org/wiki/Hierarchy_of_angels</t>
         </is>
       </c>
       <c r="R64" s="6" t="inlineStr"/>
@@ -5592,7 +5580,7 @@
       <c r="P65" s="6" t="inlineStr"/>
       <c r="Q65" s="8" t="inlineStr">
         <is>
-          <t>HTTP 404</t>
+          <t>https://en.wikipedia.org/wiki/HTTP_404</t>
         </is>
       </c>
       <c r="R65" s="6" t="inlineStr"/>
@@ -5662,7 +5650,7 @@
       <c r="P66" s="6" t="inlineStr"/>
       <c r="Q66" s="8" t="inlineStr">
         <is>
-          <t>Hyper Text Coffee Pot Control Protocol</t>
+          <t>https://en.wikipedia.org/wiki/Hyper_Text_Coffee_Pot_Control_Protocol</t>
         </is>
       </c>
       <c r="R66" s="6" t="inlineStr">
@@ -5736,7 +5724,7 @@
       <c r="P67" s="6" t="inlineStr"/>
       <c r="Q67" s="8" t="inlineStr">
         <is>
-          <t>Fahrenheit 451</t>
+          <t>https://en.wikipedia.org/wiki/Fahrenheit_451</t>
         </is>
       </c>
       <c r="R67" s="6" t="inlineStr"/>
@@ -5806,7 +5794,7 @@
       <c r="P68" s="6" t="inlineStr"/>
       <c r="Q68" s="8" t="inlineStr">
         <is>
-          <t>47 (number)</t>
+          <t>https://en.wikipedia.org/wiki/47_%28number%29</t>
         </is>
       </c>
       <c r="R68" s="6" t="inlineStr">
@@ -5880,7 +5868,7 @@
       <c r="P69" s="6" t="inlineStr"/>
       <c r="Q69" s="8" t="inlineStr">
         <is>
-          <t>Localhost</t>
+          <t>https://en.wikipedia.org/wiki/Localhost</t>
         </is>
       </c>
       <c r="R69" s="6" t="inlineStr"/>
@@ -5950,7 +5938,7 @@
       <c r="P70" s="6" t="inlineStr"/>
       <c r="Q70" s="8" t="inlineStr">
         <is>
-          <t>17 (number)</t>
+          <t>https://en.wikipedia.org/wiki/17_%28number%29</t>
         </is>
       </c>
       <c r="R70" s="6" t="inlineStr"/>
@@ -6028,7 +6016,7 @@
       </c>
       <c r="Q71" s="8" t="inlineStr">
         <is>
-          <t>73 (number)</t>
+          <t>https://en.wikipedia.org/wiki/73_%28number%29</t>
         </is>
       </c>
       <c r="R71" s="6" t="inlineStr">
@@ -6102,7 +6090,7 @@
       <c r="P72" s="6" t="inlineStr"/>
       <c r="Q72" s="8" t="inlineStr">
         <is>
-          <t>A440 (pitch standard)</t>
+          <t>https://en.wikipedia.org/wiki/A440_%28pitch_standard%29</t>
         </is>
       </c>
       <c r="R72" s="6" t="inlineStr"/>
@@ -6176,7 +6164,7 @@
       </c>
       <c r="Q73" s="8" t="inlineStr">
         <is>
-          <t>Speed of light</t>
+          <t>https://en.wikipedia.org/wiki/Speed_of_light</t>
         </is>
       </c>
       <c r="R73" s="6" t="inlineStr"/>
@@ -6250,7 +6238,7 @@
       </c>
       <c r="Q74" s="8" t="inlineStr">
         <is>
-          <t>Conventional memory</t>
+          <t>https://en.wikipedia.org/wiki/Conventional_memory</t>
         </is>
       </c>
       <c r="R74" s="6" t="inlineStr">
@@ -6324,7 +6312,7 @@
       <c r="P75" s="6" t="inlineStr"/>
       <c r="Q75" s="8" t="inlineStr">
         <is>
-          <t>Human skeleton</t>
+          <t>https://en.wikipedia.org/wiki/Human_skeleton</t>
         </is>
       </c>
       <c r="R75" s="6" t="inlineStr"/>
@@ -6398,7 +6386,7 @@
       </c>
       <c r="Q76" s="8" t="inlineStr">
         <is>
-          <t>Chromosome</t>
+          <t>https://en.wikipedia.org/wiki/Chromosome</t>
         </is>
       </c>
       <c r="R76" s="6" t="inlineStr"/>
@@ -6468,7 +6456,7 @@
       <c r="P77" s="6" t="inlineStr"/>
       <c r="Q77" s="8" t="inlineStr">
         <is>
-          <t>Periodic table</t>
+          <t>https://en.wikipedia.org/wiki/Periodic_table</t>
         </is>
       </c>
       <c r="R77" s="6" t="inlineStr"/>
@@ -6538,7 +6526,7 @@
       <c r="P78" s="6" t="inlineStr"/>
       <c r="Q78" s="8" t="inlineStr">
         <is>
-          <t>Kelvin</t>
+          <t>https://en.wikipedia.org/wiki/Kelvin</t>
         </is>
       </c>
       <c r="R78" s="6" t="inlineStr"/>
@@ -6608,7 +6596,7 @@
       <c r="P79" s="6" t="inlineStr"/>
       <c r="Q79" s="8" t="inlineStr">
         <is>
-          <t>Human body temperature</t>
+          <t>https://en.wikipedia.org/wiki/Human_body_temperature</t>
         </is>
       </c>
       <c r="R79" s="6" t="inlineStr"/>
@@ -6678,7 +6666,7 @@
       <c r="P80" s="6" t="inlineStr"/>
       <c r="Q80" s="8" t="inlineStr">
         <is>
-          <t>Fahrenheit</t>
+          <t>https://en.wikipedia.org/wiki/Fahrenheit</t>
         </is>
       </c>
       <c r="R80" s="6" t="inlineStr"/>
@@ -6748,7 +6736,7 @@
       <c r="P81" s="6" t="inlineStr"/>
       <c r="Q81" s="8" t="inlineStr">
         <is>
-          <t>Tropical year</t>
+          <t>https://en.wikipedia.org/wiki/Tropical_year</t>
         </is>
       </c>
       <c r="R81" s="6" t="inlineStr">
@@ -6822,7 +6810,7 @@
       <c r="P82" s="6" t="inlineStr"/>
       <c r="Q82" s="8" t="inlineStr">
         <is>
-          <t>Leap year</t>
+          <t>https://en.wikipedia.org/wiki/Leap_year</t>
         </is>
       </c>
       <c r="R82" s="6" t="inlineStr"/>
@@ -6892,7 +6880,7 @@
       <c r="P83" s="6" t="inlineStr"/>
       <c r="Q83" s="8" t="inlineStr">
         <is>
-          <t>Month</t>
+          <t>https://en.wikipedia.org/wiki/Month</t>
         </is>
       </c>
       <c r="R83" s="6" t="inlineStr">
@@ -6966,7 +6954,7 @@
       <c r="P84" s="6" t="inlineStr"/>
       <c r="Q84" s="8" t="inlineStr">
         <is>
-          <t>Lunar month</t>
+          <t>https://en.wikipedia.org/wiki/Lunar_month</t>
         </is>
       </c>
       <c r="R84" s="6" t="inlineStr"/>
@@ -7036,7 +7024,7 @@
       <c r="P85" s="6" t="inlineStr"/>
       <c r="Q85" s="8" t="inlineStr">
         <is>
-          <t>Metonic cycle</t>
+          <t>https://en.wikipedia.org/wiki/Metonic_cycle</t>
         </is>
       </c>
       <c r="R85" s="6" t="inlineStr">
@@ -7114,7 +7102,7 @@
       </c>
       <c r="Q86" s="8" t="inlineStr">
         <is>
-          <t>Week</t>
+          <t>https://en.wikipedia.org/wiki/Week</t>
         </is>
       </c>
       <c r="R86" s="6" t="inlineStr"/>
@@ -7188,7 +7176,7 @@
       </c>
       <c r="Q87" s="8" t="inlineStr">
         <is>
-          <t>February</t>
+          <t>https://en.wikipedia.org/wiki/February</t>
         </is>
       </c>
       <c r="R87" s="6" t="inlineStr"/>
@@ -7258,7 +7246,7 @@
       <c r="P88" s="6" t="inlineStr"/>
       <c r="Q88" s="8" t="inlineStr">
         <is>
-          <t>Gregorian calendar</t>
+          <t>https://en.wikipedia.org/wiki/Gregorian_calendar</t>
         </is>
       </c>
       <c r="R88" s="6" t="inlineStr"/>
@@ -7328,7 +7316,7 @@
       <c r="P89" s="6" t="inlineStr"/>
       <c r="Q89" s="8" t="inlineStr">
         <is>
-          <t>911 (emergency telephone number)</t>
+          <t>https://en.wikipedia.org/wiki/911_%28emergency_telephone_number%29</t>
         </is>
       </c>
       <c r="R89" s="6" t="inlineStr">
@@ -7402,7 +7390,7 @@
       <c r="P90" s="6" t="inlineStr"/>
       <c r="Q90" s="8" t="inlineStr">
         <is>
-          <t>Fictitious telephone number</t>
+          <t>https://en.wikipedia.org/wiki/Fictitious_telephone_number</t>
         </is>
       </c>
       <c r="R90" s="6" t="inlineStr">
@@ -7476,7 +7464,7 @@
       <c r="P91" s="6" t="inlineStr"/>
       <c r="Q91" s="8" t="inlineStr">
         <is>
-          <t>Area codes 212, 646, and 332</t>
+          <t>https://en.wikipedia.org/wiki/Area_codes_212%2C_646%2C_and_332</t>
         </is>
       </c>
       <c r="R91" s="6" t="inlineStr">
@@ -7550,7 +7538,7 @@
       <c r="P92" s="6" t="inlineStr"/>
       <c r="Q92" s="8" t="inlineStr">
         <is>
-          <t>Area codes 713, 281, 832, 346, and 621</t>
+          <t>https://en.wikipedia.org/wiki/Area_codes_713%2C_281%2C_832%2C_346%2C_and_621</t>
         </is>
       </c>
       <c r="R92" s="6" t="inlineStr">
@@ -7624,7 +7612,7 @@
       <c r="P93" s="6" t="inlineStr"/>
       <c r="Q93" s="8" t="inlineStr">
         <is>
-          <t>Area code 901</t>
+          <t>https://en.wikipedia.org/wiki/Area_code_901</t>
         </is>
       </c>
       <c r="R93" s="6" t="inlineStr">
@@ -7698,7 +7686,7 @@
       <c r="P94" s="6" t="inlineStr"/>
       <c r="Q94" s="8" t="inlineStr">
         <is>
-          <t>Area codes 313 and 679</t>
+          <t>https://en.wikipedia.org/wiki/Area_codes_313_and_679</t>
         </is>
       </c>
       <c r="R94" s="6" t="inlineStr">
@@ -7772,7 +7760,7 @@
       <c r="P95" s="6" t="inlineStr"/>
       <c r="Q95" s="8" t="inlineStr">
         <is>
-          <t>Area codes 305, 786, and 645</t>
+          <t>https://en.wikipedia.org/wiki/Area_codes_305%2C_786%2C_and_645</t>
         </is>
       </c>
       <c r="R95" s="6" t="inlineStr">
@@ -7846,7 +7834,7 @@
       <c r="P96" s="6" t="inlineStr"/>
       <c r="Q96" s="8" t="inlineStr">
         <is>
-          <t>Area codes 415 and 628</t>
+          <t>https://en.wikipedia.org/wiki/Area_codes_415_and_628</t>
         </is>
       </c>
       <c r="R96" s="6" t="inlineStr">
@@ -7920,7 +7908,7 @@
       <c r="P97" s="6" t="inlineStr"/>
       <c r="Q97" s="8" t="inlineStr">
         <is>
-          <t>Area code 808</t>
+          <t>https://en.wikipedia.org/wiki/Area_code_808</t>
         </is>
       </c>
       <c r="R97" s="6" t="inlineStr">
@@ -7994,7 +7982,7 @@
       <c r="P98" s="6" t="inlineStr"/>
       <c r="Q98" s="8" t="inlineStr">
         <is>
-          <t>Area code 504</t>
+          <t>https://en.wikipedia.org/wiki/Area_code_504</t>
         </is>
       </c>
       <c r="R98" s="6" t="inlineStr">
@@ -8068,7 +8056,7 @@
       <c r="P99" s="6" t="inlineStr"/>
       <c r="Q99" s="8" t="inlineStr">
         <is>
-          <t>Golden angle</t>
+          <t>https://en.wikipedia.org/wiki/Golden_angle</t>
         </is>
       </c>
       <c r="R99" s="6" t="inlineStr">
@@ -8142,7 +8130,7 @@
       <c r="P100" s="6" t="inlineStr"/>
       <c r="Q100" s="8" t="inlineStr">
         <is>
-          <t>Pi</t>
+          <t>https://en.wikipedia.org/wiki/Pi</t>
         </is>
       </c>
       <c r="R100" s="6" t="inlineStr">
@@ -8216,7 +8204,7 @@
       <c r="P101" s="6" t="inlineStr"/>
       <c r="Q101" s="8" t="inlineStr">
         <is>
-          <t>Tau (mathematics)</t>
+          <t>https://en.wikipedia.org/wiki/Tau_%28mathematics%29</t>
         </is>
       </c>
       <c r="R101" s="6" t="inlineStr"/>
@@ -8286,7 +8274,7 @@
       <c r="P102" s="6" t="inlineStr"/>
       <c r="Q102" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>https://en.wikipedia.org/wiki/1</t>
         </is>
       </c>
       <c r="R102" s="6" t="inlineStr">
@@ -8370,7 +8358,7 @@
       <c r="P103" s="6" t="inlineStr"/>
       <c r="Q103" s="8" t="inlineStr">
         <is>
-          <t>Fundamental theorem of arithmetic</t>
+          <t>https://en.wikipedia.org/wiki/Fundamental_theorem_of_arithmetic</t>
         </is>
       </c>
       <c r="R103" s="6" t="inlineStr">
@@ -8497,7 +8485,7 @@
       </c>
       <c r="H105" s="6" t="inlineStr">
         <is>
-          <t>NEEDS A THIRD DROP - see Distribution</t>
+          <t>WHOLE!</t>
         </is>
       </c>
       <c r="I105" s="6" t="inlineStr">
@@ -8535,7 +8523,7 @@
       <c r="Q105" s="6" t="inlineStr"/>
       <c r="R105" s="6" t="inlineStr">
         <is>
-          <t>ACCEPTED by Dakota. Note this is the row that puts the total at 102 - it needs a third drop to fund it. Also now doubles as the discoverability half of the "tap an achievement to view it in the trophy room" change; see the UI changes tab. CODE: the cup already exists as a control, so this is a dom trigger on it through the existing onTrusted delegation - nothing new to wire.</t>
+          <t>ACCEPTED by Dakota, and funded by dropping WHOLE! - see that row. Also the discoverability half of the "tap an achievement to view it in the trophy room" change; see the UI changes tab. CODE: the cup already exists as a control, so this is a dom trigger on it through the existing onTrusted delegation - nothing new to wire.</t>
         </is>
       </c>
     </row>
@@ -8866,83 +8854,79 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q23" r:id="rId10"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q24" r:id="rId11"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q25" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q26" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q27" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q28" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q29" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q30" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q31" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q32" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q33" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q34" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q35" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q36" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q37" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q38" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q39" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q40" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q41" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q43" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q44" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q45" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q46" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q47" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q48" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q49" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q50" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q51" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q52" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q53" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q54" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q55" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q56" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q57" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q58" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q59" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q60" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q61" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q62" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q63" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q64" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q65" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q66" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q67" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q68" r:id="rId54"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q69" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q70" r:id="rId56"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q71" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q72" r:id="rId58"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q73" r:id="rId59"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q74" r:id="rId60"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q75" r:id="rId61"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q76" r:id="rId62"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q77" r:id="rId63"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q78" r:id="rId64"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q79" r:id="rId65"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q80" r:id="rId66"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q81" r:id="rId67"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q82" r:id="rId68"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q83" r:id="rId69"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q84" r:id="rId70"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q85" r:id="rId71"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q86" r:id="rId72"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q87" r:id="rId73"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q88" r:id="rId74"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q89" r:id="rId75"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q90" r:id="rId76"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q91" r:id="rId77"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q92" r:id="rId78"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q93" r:id="rId79"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q94" r:id="rId80"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q95" r:id="rId81"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q96" r:id="rId82"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q97" r:id="rId83"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q98" r:id="rId84"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q99" r:id="rId85"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q100" r:id="rId86"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q101" r:id="rId87"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q102" r:id="rId88"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q103" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q27" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q28" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q29" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q30" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q31" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q32" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q33" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q34" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q35" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q36" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q37" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q38" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q39" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q41" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q44" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q45" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q46" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q47" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q48" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q49" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q50" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q51" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q52" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q53" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q54" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q55" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q56" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q57" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q58" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q60" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q61" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q62" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q63" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q64" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q65" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q66" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q67" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q68" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q69" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q70" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q71" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q72" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q73" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q74" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q75" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q76" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q77" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q78" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q79" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q80" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q81" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q82" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q83" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q84" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q85" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q86" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q87" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q88" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q89" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q90" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q91" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q92" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q93" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q94" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q95" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q96" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q97" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q98" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q99" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q100" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q101" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q102" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q103" r:id="rId85"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -8954,7 +8938,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G49"/>
+  <dimension ref="A1:G44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -9446,7 +9430,7 @@
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>DECISION NEEDED: the list is at 102, not 101.</t>
+          <t>SETTLED: the list balances at 101.</t>
         </is>
       </c>
     </row>
@@ -9456,7 +9440,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>You accepted GALLERY! and rejected DOUBLING! and THIRD!. That leaves three additions (DECOMPOSE!, TEMPTED!, GALLERY!) funded by two drops (CEILING!, MERSENNE!), so the total is 102 and XP is 2015 against a hard cap of 2000. One more drop is needed.</t>
+          <t>GALLERY! was accepted and DOUBLING! and THIRD! rejected, which briefly put the list at 102. Dakota resolved it by dropping WHOLE! - the most inside reference in the list, and the only one with no blurb at all, so a player who did not already know Thelema got the clue and the number 93 and no way to close the gap. It was the clearest case of the education tax the rubric exists to prevent, which made it the right third drop rather than merely an available one.</t>
         </is>
       </c>
     </row>
@@ -9464,30 +9448,22 @@
       <c r="A25" s="2" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="4" t="inlineStr">
-        <is>
-          <t>Ranked candidates, all currently marked REVIEW on the Proposal tab:</t>
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>Final shape: three drops (CEILING!, MERSENNE!, WHOLE!), three additions (DECOMPOSE!, TEMPTED!, GALLERY!), seven in-place fixes. 101 achievements, 2000 XP, 18 Revealed and 83 Hidden. All of it is built, checked and verified on a Pixel 7.</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  1. GRACELAND! (901). The thinnest entry in the list - the blurb is one sentence, '901 is Memphis', and Elvis is the only hook. Nothing else in the design depends on it. This is my recommendation.</t>
-        </is>
-      </c>
+      <c r="A27" s="2" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  2. SUPERPRIME!. Worst effort-to-payoff ratio in the list: 11 taps returning the same 11 nodes, and no gild set can fix it. Costs you a genuinely intuitive idea, which is why it is second rather than first.</t>
-        </is>
-      </c>
+      <c r="A28" s="2" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  3. MEME! (67). The entry that ages fastest, and Play Games will not let you remove it later. Dropping it now is the only chance you get.</t>
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>Is the balance reasonable? Mostly yes, with two exceptions.</t>
         </is>
       </c>
     </row>
@@ -9497,7 +9473,7 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>I have NOT applied any of these - Scenario A still reads 102 so the gap stays visible. Flip one In A? cell to N and every count on this tab follows.</t>
+          <t>Culture is 61% of the list (62 of 101). That is defensible: the Culture mechanic - recognise a number, work out its prime factors, watch it come apart - IS the app's core loop, and it is the most newbie-accessible thing in the design. Repeating it 62 times with good material is a reasonable bet.</t>
         </is>
       </c>
     </row>
@@ -9505,32 +9481,40 @@
       <c r="A32" s="2" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="inlineStr"/>
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>Math is 22% (22 of 101) for an app about integers. Lower than you might expect, but the Math entries carry far more weight per achievement - the relational ones gild 37 to 120 nodes each. I would not grow Math for its own sake; I would grow Puzzles and Greeks specifically, because those two are where 'intuition about integers' actually lives.</t>
+        </is>
+      </c>
     </row>
     <row r="34">
-      <c r="A34" s="4" t="inlineStr">
-        <is>
-          <t>Is the balance reasonable? Mostly yes, with two exceptions.</t>
-        </is>
-      </c>
+      <c r="A34" s="2" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="inlineStr"/>
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>Dial is the exception worth acting on. 10 of 101 - a tenth of the entire list - and:</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>Culture is 61% of the list (62 of 101). That is defensible: the Culture mechanic - recognise a number, work out its prime factors, watch it come apart - IS the app's core loop, and it is the most newbie-accessible thing in the design. Repeating it 62 times with good material is a reasonable bet.</t>
+          <t xml:space="preserve">  - No integer content whatsoever. The trigger is typing a number into a slider, which is the exact thing §1 calls 'entering a password' when it explains why twelve set-the-range achievements were cut. Dial is rescued by a fiction ('a phone number is a thing you dial'), and the fiction is charming, but it buys mechanics rather than meaning.</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="inlineStr"/>
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - The payoff is flat every single time. You type 713, and 713 lights up. Ten consecutive 'huh, yeah I guess' moments.</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>Math is 22% (22 of 101) for an app about integers. Lower than you might expect, but the Math entries carry far more weight per achievement - the relational ones gild 37 to 120 nodes each. I would not grow Math for its own sake; I would grow Puzzles and Greeks specifically, because those two are where 'intuition about integers' actually lives.</t>
+          <t xml:space="preserve">  - It fails your rubric in a second way you did not name. Six of the ten are US area codes with no meaning outside America. A player in Manchester or Osaka does not feel under-educated, they feel excluded - which lands in the same place.</t>
         </is>
       </c>
     </row>
@@ -9540,63 +9524,32 @@
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>Dial is the exception worth acting on. 10 of 101 - a tenth of the entire list - and:</t>
+          <t>Recommendation: keep 5, drop 5. Keep HELP! (911), CENTRAL! (555), NY! (212), ALOHA! (808) and MOTOR CITY! (313) - each has recognition or a second meaning that travels. Drop SPACE CITY!, GRACELAND!, VICE!, BAY! and NOLA!, which are area-code trivia and nothing else. That preserves the Dial mechanic and the joke while cutting its cost in half.</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  - No integer content whatsoever. The trigger is typing a number into a slider, which is the exact thing §1 calls 'entering a password' when it explains why twelve set-the-range achievements were cut. Dial is rescued by a fiction ('a phone number is a thing you dial'), and the fiction is charming, but it buys mechanics rather than meaning.</t>
-        </is>
-      </c>
+      <c r="A41" s="2" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  - The payoff is flat every single time. You type 713, and 713 lights up. Ten consecutive 'huh, yeah I guess' moments.</t>
+          <t>The arithmetic, updated for your decisions: dropping 5 from Dial frees 5 slots. One is already spoken for by GALLERY! above. DOUBLING! and THIRD! are rejected, so the remaining 4 have no designed replacement - that is design work I have not done. So the Dial cut stays a separate decision rather than a bundled one, and if you want it, tell me how many slots to fill and I will draft candidates for Puzzles.</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  - It fails your rubric in a second way you did not name. Six of the ten are US area codes with no meaning outside America. A player in Manchester or Osaka does not feel under-educated, they feel excluded - which lands in the same place.</t>
-        </is>
-      </c>
+      <c r="A43" s="2" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="2" t="inlineStr"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="4" t="inlineStr">
-        <is>
-          <t>Recommendation: keep 5, drop 5. Keep HELP! (911), CENTRAL! (555), NY! (212), ALOHA! (808) and MOTOR CITY! (313) - each has recognition or a second meaning that travels. Drop SPACE CITY!, GRACELAND!, VICE!, BAY! and NOLA!, which are area-code trivia and nothing else. That preserves the Dial mechanic and the joke while cutting its cost in half.</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="2" t="inlineStr">
-        <is>
-          <t>The arithmetic, updated for your decisions: dropping 5 from Dial frees 5 slots. One is already spoken for by GALLERY! above. DOUBLING! and THIRD! are rejected, so the remaining 4 have no designed replacement - that is design work I have not done. So the Dial cut stays a separate decision rather than a bundled one, and if you want it, tell me how many slots to fill and I will draft candidates for Puzzles.</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="2" t="inlineStr"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="2" t="inlineStr">
+      <c r="A44" s="2" t="inlineStr">
         <is>
           <t>One more, not a distribution point: 13 of the 101 have no blurb at all, 12 of them in Meme and Lore. When we come back to the Wikipedia links, those 13 are the ones that need it most - for them the link is not a footnote, it is the entire explanation.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="29">
+  <mergeCells count="24">
     <mergeCell ref="A32:G32"/>
     <mergeCell ref="E19:G19"/>
     <mergeCell ref="A22:G22"/>
@@ -9610,20 +9563,15 @@
     <mergeCell ref="A31:G31"/>
     <mergeCell ref="A39:G39"/>
     <mergeCell ref="A34:G34"/>
-    <mergeCell ref="A48:G48"/>
     <mergeCell ref="A24:G24"/>
     <mergeCell ref="A30:G30"/>
-    <mergeCell ref="A49:G49"/>
-    <mergeCell ref="A45:G45"/>
     <mergeCell ref="A36:G36"/>
     <mergeCell ref="A25:G25"/>
     <mergeCell ref="A41:G41"/>
     <mergeCell ref="A37:G37"/>
-    <mergeCell ref="A46:G46"/>
     <mergeCell ref="A27:G27"/>
     <mergeCell ref="A26:G26"/>
     <mergeCell ref="A33:G33"/>
-    <mergeCell ref="A47:G47"/>
     <mergeCell ref="A42:G42"/>
     <mergeCell ref="A23:G23"/>
   </mergeCells>
@@ -9954,7 +9902,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -10145,7 +10093,7 @@
     <row r="24">
       <c r="A24" s="25" t="inlineStr">
         <is>
-          <t>Back on. 89 of 104 get one, and every title is verified against the live Wikipedia API.</t>
+          <t>Shipped. 85 of the 101 carry one, every title verified against the live Wikipedia API.</t>
         </is>
       </c>
     </row>
@@ -10157,67 +10105,79 @@
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>89 of 104 achievements have a proposed link, in the 'Proposed link' column on the Proposal tab. The other 15 are jokes or UI furniture where no article adds anything - ORBS!, TRIPPY!, MEME! and so on.</t>
+          <t>85 of the 101 shipped achievements carry a link, in the 'Proposed link' column on the Proposal tab, which reads from the shipped data file. The rest are jokes a footnote would only flatten - ORBS!, TRIPPY!, MEME! and so on.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="7" t="inlineStr">
         <is>
-          <t>Verified, not guessed</t>
+          <t>Content rating - added after the first pass</t>
         </is>
       </c>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>All 86 distinct article titles were checked against the Wikipedia API: every one exists, resolves directly, and none is a redirect or a disambiguation page. Eleven were corrected during that pass - CENTRAL! had been pointing at a disambiguation page, and every area-code article has been renamed since.</t>
+          <t>A link is a machine-readable assertion in a way a number is not. 420 under the clue '-what was I saying?-' is a number; a link to '420 (cannabis culture)' is documentary evidence of a drug reference in the shipped bundle, and the IARC questionnaire asks about exactly that. Six links were retargeted to the neutral number article (DUDE! 420, JACKPOT! 777, CARDS! 21, ENIGMA! 23, MASONIC! 33, and SATOR! to Palindromic number) and two dropped outright (NICE!, OIL!). The checker now scans every link against a token denylist and pins the six retargets.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="7" t="inlineStr">
         <is>
-          <t>Store it as a field, not inline HTML</t>
+          <t>Verified, not guessed</t>
         </is>
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>Put the article title, or the full URL, in its own `link` field. Blurbs are shared with the Play Console paste through tools/achievements-table.mjs, so markup written into blurb text would leak straight into that column.</t>
+          <t>All 86 distinct article titles were checked against the Wikipedia API: every one exists, resolves directly, and none is a redirect or a disambiguation page. Eleven were corrected during that pass - CENTRAL! had been pointing at a disambiguation page, and every area-code article has been renamed since.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="7" t="inlineStr">
         <is>
-          <t>The plumbing decision is still real</t>
+          <t>Store it as a field, not inline HTML</t>
         </is>
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>The app has no external links anywhere today, and @capacitor/browser is NOT installed - package.json carries only @capacitor/android and @capacitor/core. A bare &lt;a href&gt; inside the WebView navigates the app away with no way back, so this needs the Browser plugin or an appUrlOpen handler before the first link ships.</t>
+          <t>Put the article title, or the full URL, in its own `link` field. Blurbs are shared with the Play Console paste through tools/achievements-table.mjs, so markup written into blurb text would leak straight into that column.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="7" t="inlineStr">
         <is>
-          <t>Checker</t>
+          <t>The plumbing turned out to be free - confirmed on a Pixel 7</t>
         </is>
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>Assert every link is https, and that all 13 blurb-less achievements have one. A periodic title re-check is cheap: the whole set is two API calls.</t>
+          <t>Bridge.launchIntent() fires an ACTION_VIEW intent for any URL whose host is neither the app host nor in allowNavigation, and capacitor.config.json sets no allowNavigation at all. setSupportMultipleWindows is left at its default of false, so a target=_blank link navigates in place and reaches shouldOverrideUrlLoading, which calls that intent. Tapping REST!'s link brought Chrome to the foreground with the app still resident behind it. @capacitor/browser stays uninstalled.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="7" t="inlineStr">
         <is>
+          <t>Checker</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="inlineStr">
+        <is>
+          <t>Every link is asserted https and Wikipedia, with no raw spaces; the count is pinned; and nothing may have neither a blurb nor a link. A periodic title re-check is cheap - the whole set is two API calls.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="7" t="inlineStr">
+        <is>
           <t>Priority</t>
         </is>
       </c>
-      <c r="B30" s="6" t="inlineStr">
-        <is>
-          <t>The 13 achievements with NO blurb need this most - WHOLE!, MASONIC!, ENIGMA!, CATCH!, ROUTE!, CARDS!, JACKPOT!, SLURPEE!, JUMBO!, SPARTA!, LUCKY!, LOUDER! and MEME!. For those the link is not a footnote, it is the entire explanation.</t>
+      <c r="B31" s="6" t="inlineStr">
+        <is>
+          <t>The twelve with NO blurb need this most: LOUDER!, MEME!, CATCH!, ROUTE!, CARDS!, JACKPOT!, SLURPEE!, SPARTA!, JUMBO!, LUCKY!, ENIGMA! and MASONIC!. For those the link is not a footnote, it is the entire explanation. MEME! is the single recorded exception with neither, because an encyclopedia article cannot deliver a punchline - and WHOLE!, which was the worst case of all, was dropped rather than explained.</t>
         </is>
       </c>
     </row>
